--- a/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/NhapThongTinNguoiPhuThuoc.xlsx
+++ b/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/NhapThongTinNguoiPhuThuoc.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SourceCodeHR\SnK_Dev\SmartBooks.HumanResource\bin\x86\Debug\Teamleate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE7947F-29A3-45E2-8F39-11E282371189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE49898-DCCD-49E0-982E-C150A5F282EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
   <si>
     <t>Danh Sách Người Phụ Thuộc</t>
   </si>
@@ -157,23 +170,35 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>Code_</t>
-  </si>
-  <si>
-    <t>Name_</t>
-  </si>
-  <si>
-    <t>Mã code</t>
-  </si>
-  <si>
-    <t>Giá trị</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Cha</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Mẹ</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Con</t>
+  </si>
+  <si>
+    <t>Khác</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -182,20 +207,16 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -205,12 +226,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -246,7 +261,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -265,9 +280,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -305,7 +320,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -411,7 +426,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -553,7 +568,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -561,33 +576,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:X10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:V10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="7" width="9.140625" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" customWidth="1"/>
-    <col min="14" max="14" width="16.42578125" customWidth="1"/>
-    <col min="15" max="15" width="15.28515625" customWidth="1"/>
-    <col min="16" max="16" width="11.5703125" customWidth="1"/>
-    <col min="17" max="17" width="10" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" customWidth="1"/>
-    <col min="19" max="19" width="9.5703125" customWidth="1"/>
-    <col min="20" max="20" width="11.7109375" customWidth="1"/>
-    <col min="21" max="21" width="18.7109375" customWidth="1"/>
-    <col min="22" max="22" width="20.140625" customWidth="1"/>
-    <col min="23" max="23" width="12" customWidth="1"/>
-    <col min="24" max="24" width="9.140625" customWidth="1"/>
+    <col min="4" max="5" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" customWidth="1"/>
+    <col min="17" max="17" width="9.5703125" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" customWidth="1"/>
+    <col min="19" max="19" width="18.7109375" customWidth="1"/>
+    <col min="20" max="20" width="20.140625" customWidth="1"/>
+    <col min="21" max="21" width="12" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:24" ht="18.75">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -600,27 +631,39 @@
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="G3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="5" spans="1:24" hidden="1">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
-      <c r="I5" t="s">
+      <c r="G5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:24" hidden="1">
+    <row r="6" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -633,70 +676,64 @@
       <c r="D6" t="s">
         <v>5</v>
       </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
       <c r="G6" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="U6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V6" t="s">
-        <v>20</v>
-      </c>
-      <c r="W6" t="s">
-        <v>21</v>
-      </c>
-      <c r="X6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:24" hidden="1">
-      <c r="E7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24">
+    <row r="7" spans="1:22" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:22" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -709,70 +746,64 @@
       <c r="D10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="F10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="H10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X10" s="2" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
